--- a/output/pdf_financials_xlsx/GC.xlsx
+++ b/output/pdf_financials_xlsx/GC.xlsx
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.00094</v>
+        <v>0.131307</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.005</v>
+        <v>0.143074</v>
       </c>
     </row>
     <row r="11">
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.008475999999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.223857</v>
       </c>
     </row>
     <row r="35">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.008475999999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.223857</v>
       </c>
     </row>
     <row r="37">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.008503</v>
+        <v>2.7e-05</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.223857</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E44" s="5" t="n">

--- a/output/pdf_financials_xlsx/GC.xlsx
+++ b/output/pdf_financials_xlsx/GC.xlsx
@@ -1868,7 +1868,7 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.0032</v>
       </c>
     </row>
     <row r="111">
@@ -2740,7 +2740,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
